--- a/product_upload/packages/23/file.xlsx
+++ b/product_upload/packages/23/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -836,6 +841,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>FEVADOL 200MG SUPPOSITORY</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-F83DC70791B1</t>
         </is>
       </c>
@@ -859,7 +869,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1018,6 +1028,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>FEVADOL 100MG SUPPOSITORY</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-BD7636003FA4</t>
         </is>
       </c>
@@ -1041,7 +1056,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1208,6 +1223,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>FERTAB 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-60AF58738F2A</t>
         </is>
       </c>
@@ -1231,7 +1251,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1398,6 +1418,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>FERRO-FOL CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-6ED8FEEBF012</t>
         </is>
       </c>
@@ -1421,7 +1446,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1592,6 +1617,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>FERRIPROX 100MG/ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-13C2B573850F</t>
         </is>
       </c>
@@ -1615,7 +1645,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1778,6 +1808,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>FEROSE TAB (EQV.TO 100MG OF IRON)</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-BEAEBC062C57</t>
         </is>
       </c>
@@ -1801,7 +1836,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1970,6 +2005,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>FEVADOL PLUS TAB</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-07CB18C64127</t>
         </is>
       </c>
@@ -1993,7 +2033,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2152,6 +2192,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>FEVADOL SF 120MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-EBC2CE13DDCD</t>
         </is>
       </c>
@@ -2175,7 +2220,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2338,6 +2383,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>FEVADOL SF 120MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-63D05D5DAA8C</t>
         </is>
       </c>
@@ -2361,7 +2411,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2524,6 +2574,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>FEVADOL SYRUP 120MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-C32C156DD4E8</t>
         </is>
       </c>
@@ -2547,7 +2602,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2710,6 +2765,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>FIXIT 300MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-9F38F776ABA5</t>
         </is>
       </c>
@@ -2733,7 +2793,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2900,6 +2960,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>FIXIT 150MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-48E16C44C7C8</t>
         </is>
       </c>
@@ -2923,7 +2988,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3090,6 +3155,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>FIXIT 150MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-E712CB5F4E0C</t>
         </is>
       </c>
@@ -3113,7 +3183,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3272,6 +3342,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>FEROSE SYRUP 50MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-C2A5211E2709</t>
         </is>
       </c>
@@ -3295,7 +3370,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3466,6 +3541,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>FINISCAR 5MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-52505A5A8EA8</t>
         </is>
       </c>
@@ -3489,7 +3569,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3652,6 +3732,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>FINALLERG 1MG-1ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-73EB4DD7F678</t>
         </is>
       </c>
@@ -3675,7 +3760,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3842,6 +3927,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>FINALLERG 10MG F.C TABLET</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-3E37DFDF3FD0</t>
         </is>
       </c>
@@ -3865,7 +3955,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4032,6 +4122,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>FEXOTEL 120MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-6E5F34406D0D</t>
         </is>
       </c>
@@ -4055,7 +4150,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4226,6 +4321,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>FEXODINE 180MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-864C9FA6F2D8</t>
         </is>
       </c>
@@ -4249,7 +4349,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4420,6 +4520,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>FEXODINE 120MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-140B2604B689</t>
         </is>
       </c>
@@ -4443,7 +4548,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4614,6 +4719,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>FEVADOL SYRUP 160MG-5ML SUGAR FREE</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-AB461E8FE155</t>
         </is>
       </c>
@@ -4637,7 +4747,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4800,6 +4910,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>FEVADOL SYRUP 160MG-5ML SUGAR FREE</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-2415B894DA75</t>
         </is>
       </c>
@@ -4823,7 +4938,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4994,6 +5109,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>FINASID 5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-BB0CABADA3C9</t>
         </is>
       </c>
@@ -5017,7 +5137,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5176,6 +5296,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>FENAM 250MG TAB</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-581A143FED87</t>
         </is>
       </c>
@@ -5199,7 +5324,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5358,6 +5483,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>FENADEX 180MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-1463AF601649</t>
         </is>
       </c>
@@ -5381,7 +5511,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5544,6 +5674,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>FENADEX 120 MG F- CTABLETS</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-6DF34EC93B04</t>
         </is>
       </c>
@@ -5567,7 +5702,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5736,6 +5871,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>FEMOSTON 2-10 TABLET</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-49FAA216E40F</t>
         </is>
       </c>
@@ -5759,7 +5899,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5920,6 +6060,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>FEMOSTON 1-5 TABLET</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-0369C857DD5E</t>
         </is>
       </c>
@@ -5943,7 +6088,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6108,6 +6253,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>FEMOSTON 1-10 TABLET</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-5C7EECE62AD3</t>
         </is>
       </c>
@@ -6131,7 +6281,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6290,6 +6440,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>FELDENE 20MG DISPERSABLE TAB</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-7E431CBCEE37</t>
         </is>
       </c>
@@ -6313,7 +6468,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6480,6 +6635,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>FAWAR LEMON EFFERVESCENT SALT SACHETS 5G</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-22C786E71446</t>
         </is>
       </c>
@@ -6503,7 +6663,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6666,6 +6826,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>FAWAR FRUIT EFFERVESCENT SALT SACHETS 5G</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-0E2B24B0E7A0</t>
         </is>
       </c>
@@ -6689,7 +6854,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6860,6 +7025,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>FENAM 50MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-C13F262A6AEF</t>
         </is>
       </c>
@@ -6883,7 +7053,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7050,6 +7220,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>FENAM FORTE 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-1F26ECB21AEF</t>
         </is>
       </c>
@@ -7073,7 +7248,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7240,6 +7415,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>FENAMIC 250 MG CAP</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-6BA1B58E8531</t>
         </is>
       </c>
@@ -7263,7 +7443,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7426,6 +7606,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>FEROMIN ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-1FD04A16A4D3</t>
         </is>
       </c>
@@ -7449,7 +7634,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7620,6 +7805,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>FEROMIN</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-8140C866B3C8</t>
         </is>
       </c>
@@ -7643,7 +7833,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7802,6 +7992,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>FER-IN-SOL DROPS 15MG-0.6ML (ELEMENTAL I</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-10D9451B7A7A</t>
         </is>
       </c>
@@ -7825,7 +8020,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7984,6 +8179,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>FEROSE - F TABLET</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-C1AAD9DEA86C</t>
         </is>
       </c>
@@ -8007,7 +8207,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8178,6 +8378,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>FENISTIL GEL</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-EC9C69D57788</t>
         </is>
       </c>
@@ -8201,7 +8406,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8376,6 +8581,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>FENISTIL DROPS 0.1G-100ML</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-3BA62113053C</t>
         </is>
       </c>
@@ -8399,7 +8609,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8558,6 +8768,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>FENOGAL 200MG LIDOSE CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-A9AFEDA423D2</t>
         </is>
       </c>
@@ -8581,7 +8796,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8754,6 +8969,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>FAVERIN 50MG EC TABS</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-C0D1BDF3D435</t>
         </is>
       </c>
@@ -8777,7 +8997,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8944,6 +9164,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>FLAMAZINE CREAM</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-AF87A43BBD0A</t>
         </is>
       </c>
@@ -8967,7 +9192,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9126,6 +9351,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>FLAMAZINE CREAM 1%</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-7BA819D05F06</t>
         </is>
       </c>
@@ -9149,7 +9379,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9320,6 +9550,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>FLUDREX SYRUP</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-22C177158EDE</t>
         </is>
       </c>
@@ -9343,7 +9578,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9502,6 +9737,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>FLUDARA 10MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-CEF7E7F2C087</t>
         </is>
       </c>
@@ -9525,7 +9765,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9692,6 +9932,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>FLUCA OPTHALMIC SUSP.</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-21ED9BFC57BA</t>
         </is>
       </c>
@@ -9715,7 +9960,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9878,6 +10123,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>FLUANXOL 3MG TAB</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-FC0F847AA67D</t>
         </is>
       </c>
@@ -9901,7 +10151,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10060,6 +10310,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>FLUANXOL 1MG TAB</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-1D69A0DEB2EF</t>
         </is>
       </c>
@@ -10083,7 +10338,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10246,6 +10501,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>FLUANXOL 0.5MG TAB</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-CC0DE103C68C</t>
         </is>
       </c>
@@ -10269,7 +10529,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10436,6 +10696,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>FLUDREX SYRUP</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-8F61AAB0F85D</t>
         </is>
       </c>
@@ -10459,7 +10724,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10634,6 +10899,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>FLUDREX TAB</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-57697A7752C4</t>
         </is>
       </c>
@@ -10657,7 +10927,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10824,6 +11094,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t xml:space="preserve">FLUIMUCIL 100MG/1GM GRANULES FOR ORAL SOLUTION </t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-C8D04AAE5CA0</t>
         </is>
       </c>
@@ -10847,7 +11122,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11010,6 +11285,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t xml:space="preserve">FLUIMUCIL 200MG/1GM GRANULES FOR ORAL SOLUTION </t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-580AF254A41B</t>
         </is>
       </c>
@@ -11033,7 +11313,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11192,6 +11472,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>FLUOXETIN HEXAL 20MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-A2899FFC08BC</t>
         </is>
       </c>
@@ -11215,7 +11500,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11374,6 +11659,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>FLUANXOL 0.5MG TAB</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-5FEEF57C1052</t>
         </is>
       </c>
@@ -11397,7 +11687,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11556,6 +11846,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>FLUORETS OPTH.STRIPS</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-1DAF2C4FAC8B</t>
         </is>
       </c>
@@ -11579,7 +11874,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11750,6 +12045,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>FLUMED DM PAED SYRUP</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-AFB38063C93E</t>
         </is>
       </c>
@@ -11773,7 +12073,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11936,6 +12236,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>FLAMAZINE CREAM 1%</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-904DDAC56B9B</t>
         </is>
       </c>
@@ -11959,7 +12264,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12128,6 +12433,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>FLIXOTIDE 125 MCG EVOHALER</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-6015E407909A</t>
         </is>
       </c>
@@ -12151,7 +12461,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12318,6 +12628,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>FLIXOTIDE 0.5MG-2ML NEBULE</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-8AE9F7D398DE</t>
         </is>
       </c>
@@ -12341,7 +12656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12508,6 +12823,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>Otri Allergy Nasal Spray</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-B16807A4E2A0</t>
         </is>
       </c>
@@ -12531,7 +12851,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12702,6 +13022,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>FLEET ENEMA</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-09B49FA9B746</t>
         </is>
       </c>
@@ -12725,7 +13050,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12888,6 +13213,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>FLEET ENEMA</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-6C8423456839</t>
         </is>
       </c>
@@ -12911,7 +13241,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13074,6 +13404,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>FLECTOR EP TISSUGEL 1GM PATCHES</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-927B5EF42FFD</t>
         </is>
       </c>
@@ -13097,7 +13432,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13268,6 +13603,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>FLAZOL 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-146C21BBD679</t>
         </is>
       </c>
@@ -13291,7 +13631,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13458,6 +13798,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>FLAZOL 125MG-5ML ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-5B618BD6D1A5</t>
         </is>
       </c>
@@ -13481,7 +13826,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13648,6 +13993,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>FLATICON 60MG CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-5E0C3E2D86C9</t>
         </is>
       </c>
@@ -13671,7 +14021,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13834,6 +14184,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>FLATICON 40MG CHEWABLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-97A5DB156B7C</t>
         </is>
       </c>
@@ -13857,7 +14212,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14012,6 +14367,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>FLIXOTIDE 2MG-2ML NEBULE</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-37A00D8D183F</t>
         </is>
       </c>
@@ -14035,7 +14395,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14204,6 +14564,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>FLIXOTIDE 50 MCG EVOHALER</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-BC2549C56316</t>
         </is>
       </c>
@@ -14227,7 +14592,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14386,6 +14751,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>FLOXAPEN SYP 125MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-E3B4F43F1B00</t>
         </is>
       </c>
@@ -14409,7 +14779,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14568,6 +14938,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>FLOXAPEN CAPS 250MG</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-4458D6206D0D</t>
         </is>
       </c>
@@ -14591,7 +14966,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14750,6 +15125,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>FLOXAPEN 500MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-BF18F3C519E2</t>
         </is>
       </c>
@@ -14773,7 +15153,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14936,6 +15316,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>FLOXAPEN 250MG-5ML POWD.FOR SUSP</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-FBDCE123F41F</t>
         </is>
       </c>
@@ -14959,7 +15344,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15130,6 +15515,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>FLOZAK</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-829F46DB6857</t>
         </is>
       </c>
@@ -15153,7 +15543,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15324,6 +15714,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>FLOCAZOLE 150 MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-4F865B21E95C</t>
         </is>
       </c>
@@ -15347,7 +15742,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15520,6 +15915,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>FLIXOTIDE EVOHALER 250MCG</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-471857B51D42</t>
         </is>
       </c>
@@ -15543,7 +15943,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15706,6 +16106,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>FLOCAZOLE 50 MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-F59A1294C902</t>
         </is>
       </c>
@@ -15729,7 +16134,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15898,6 +16303,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>FAVERIN 100MG EC TABS</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-6B6B4E701BFB</t>
         </is>
       </c>
@@ -15921,7 +16331,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16088,6 +16498,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>FATLOS 120MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-DB373CAC4DA9</t>
         </is>
       </c>
@@ -16111,7 +16526,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16274,6 +16689,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>FATLOS 120MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-F29B7873312D</t>
         </is>
       </c>
@@ -16297,7 +16717,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16464,6 +16884,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>EPANUTIN</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-F01A77A0E3A3</t>
         </is>
       </c>
@@ -16487,7 +16912,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16656,6 +17081,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>ENTAPRO 20MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-33407D3E96D6</t>
         </is>
       </c>
@@ -16679,7 +17109,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16848,6 +17278,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>ENTAPRO 10MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-3EEF05A8ADDE</t>
         </is>
       </c>
@@ -16871,7 +17306,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17046,6 +17481,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>ENEMACORT 0.02MG-ML TABLET FOR ENEMA</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-86A5F0C082C7</t>
         </is>
       </c>
@@ -17069,7 +17509,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17244,6 +17684,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>EPICOGEL SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-55C74E2C4D5D</t>
         </is>
       </c>
@@ -17267,7 +17712,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17434,6 +17879,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>EPIVIR 150MG F.C TABLET</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-1DF1423C3732</t>
         </is>
       </c>
@@ -17457,7 +17907,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17620,6 +18070,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>EPIVIR 10 MG \ ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-C69E2D77E0A4</t>
         </is>
       </c>
@@ -17643,7 +18098,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17806,6 +18261,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>EPIRAZOLE 20MG CAPS(E.C.PELLETS)</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-29C5A0932980</t>
         </is>
       </c>
@@ -17829,7 +18289,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18000,6 +18460,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>EPIMAG EFFERVESCENT GRANULE SACHET</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-70846B5E93A1</t>
         </is>
       </c>
@@ -18023,7 +18488,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18190,6 +18655,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>EPILAT 10MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-4906B033703C</t>
         </is>
       </c>
@@ -18213,7 +18683,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18380,6 +18850,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>EMICIPRO 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-800D0ADD1FCF</t>
         </is>
       </c>
@@ -18403,7 +18878,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18574,6 +19049,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>ELIQUIS 5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-612F4A60EE84</t>
         </is>
       </c>
@@ -18597,7 +19077,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18760,6 +19240,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>ELIQUIS 2.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-B399B534BB3B</t>
         </is>
       </c>
@@ -18783,7 +19268,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18958,6 +19443,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>ELIQUIS 2.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-409EEF7A5E82</t>
         </is>
       </c>
@@ -18981,7 +19471,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19148,6 +19638,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>ELIDEL 1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-D780FB61BE5D</t>
         </is>
       </c>
@@ -19171,7 +19666,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19338,6 +19833,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>ELICASAL OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-2DF7A485E9FE</t>
         </is>
       </c>
@@ -19361,7 +19861,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19527,6 +20027,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>ELICA-M CREAM</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-17271E09945C</t>
         </is>
@@ -19543,7 +20048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19589,100 +20094,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19714,7 +20224,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19729,92 +20239,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-21540</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>433.09</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>153</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19846,7 +20361,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19861,92 +20376,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-35855</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>14.01</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>154</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19978,7 +20498,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19993,92 +20513,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-16904</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>497.94</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>155</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20110,7 +20635,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20125,92 +20650,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-96122</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>265.47</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>156</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20242,7 +20772,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20257,92 +20787,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-94330</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>415.8</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>157</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20374,7 +20909,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20389,92 +20924,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-67086</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>405.36</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>158</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20506,7 +21046,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20521,92 +21061,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-63488</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>359.02</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>159</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20638,7 +21183,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20653,92 +21198,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-32713</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>146.28</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Home Health Test</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>160</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20770,7 +21320,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20785,92 +21335,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-63187</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>466.12</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Home Health Test</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>161</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20902,7 +21457,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20917,92 +21472,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-72513</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>478.97</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Home Health Test</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>162</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21034,7 +21594,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21049,92 +21609,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-10506</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>264.77</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Home Health Test</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>163</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21151,7 +21716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21257,6 +21822,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21292,7 +21867,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21357,6 +21932,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-94D6C631925C</t>
         </is>
@@ -21393,7 +21978,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21458,6 +22043,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-AEA0E5B2D168</t>
         </is>
@@ -21494,7 +22089,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21559,6 +22154,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-BE91E9D44E51</t>
         </is>
@@ -21595,7 +22200,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21660,6 +22265,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-6973B2711E00</t>
         </is>
@@ -21696,7 +22311,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21761,6 +22376,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-1A7F5428904B</t>
         </is>
@@ -21797,7 +22422,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21862,6 +22487,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-520D237ECA5C</t>
         </is>
@@ -21898,7 +22533,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21963,6 +22598,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-08A4EFA26DA9</t>
         </is>
@@ -21999,7 +22644,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22064,6 +22709,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-9A9AF0A07574</t>
         </is>
@@ -22100,7 +22755,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22165,6 +22820,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-250755D40882</t>
         </is>
@@ -22201,7 +22866,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22266,6 +22931,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-0274421D4B29</t>
         </is>
@@ -22302,7 +22977,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22367,6 +23042,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-84FA23F2C6CE</t>
         </is>
@@ -22403,7 +23088,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22468,6 +23153,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-F838F5A07AB2</t>
         </is>
@@ -22504,7 +23199,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22569,6 +23264,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-92B81B8DD91C</t>
         </is>
@@ -22605,7 +23310,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22670,6 +23375,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-46604F479477</t>
         </is>
@@ -22706,7 +23421,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22771,6 +23486,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-B29E14704A7B</t>
         </is>
@@ -22807,7 +23532,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22872,6 +23597,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-BD9C1881593C</t>
         </is>
@@ -22908,7 +23643,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22973,6 +23708,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-7D8E2D68B638</t>
         </is>
@@ -23009,7 +23754,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23074,6 +23819,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-17771EC3D091</t>
         </is>
@@ -23110,7 +23865,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23175,6 +23930,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-9A58F4313A50</t>
         </is>
@@ -23211,7 +23976,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23276,6 +24041,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-B0D0E38D330F</t>
         </is>

--- a/product_upload/packages/23/file.xlsx
+++ b/product_upload/packages/23/file.xlsx
@@ -686,8 +686,16 @@
           <t>7309347995-788-723722683304</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEVADOL 200MG SUPPOSITORY</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FEVADOL 200MG SUPPOSITORY detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -877,8 +885,16 @@
           <t>2726275868-808-315916729444</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEVADOL 100MG SUPPOSITORY</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>FEVADOL 100MG SUPPOSITORY detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -2041,8 +2057,16 @@
           <t>8596992892-402-881747647678</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEVADOL SF 120MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>FEVADOL SF 120MG\5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2228,8 +2252,16 @@
           <t>6083299660-940-087706551348</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEVADOL SF 120MG\5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>FEVADOL SF 120MG\5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2419,8 +2451,16 @@
           <t>6039836188-133-780054244067</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEVADOL SYRUP 120MG-5ML</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FEVADOL SYRUP 120MG-5ML detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -3191,8 +3231,16 @@
           <t>8569445502-565-808786141290</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEROSE SYRUP 50MG-5ML</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>FEROSE SYRUP 50MG-5ML detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3577,8 +3625,16 @@
           <t>2707781219-241-363849194863</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FINALLERG 1MG-1ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>FINALLERG 1MG-1ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3768,8 +3824,16 @@
           <t>9178593968-260-590293117894</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FINALLERG 10MG F.C TABLET</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>FINALLERG 10MG F.C TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -4755,8 +4819,16 @@
           <t>2299629214-643-887558685289</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEVADOL SYRUP 160MG-5ML SUGAR FREE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>FEVADOL SYRUP 160MG-5ML SUGAR FREE detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -5145,8 +5217,16 @@
           <t>5299146456-448-632992903637</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FENAM 250MG TAB</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>FENAM 250MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5332,8 +5412,16 @@
           <t>0964548675-286-852691608833</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FENADEX 180MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>FENADEX 180MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5519,8 +5607,16 @@
           <t>1401843664-562-486032203756</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FENADEX 120 MG F- CTABLETS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>FENADEX 120 MG F- CTABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5907,8 +6003,16 @@
           <t>0606491703-773-478020975651</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEMOSTON 1-5 TABLET</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>FEMOSTON 1-5 TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -6096,8 +6200,16 @@
           <t>0619503819-464-938851977184</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEMOSTON 1-10 TABLET</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>FEMOSTON 1-10 TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -6289,8 +6401,16 @@
           <t>4513280977-323-809216835931</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FELDENE 20MG DISPERSABLE TAB</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>FELDENE 20MG DISPERSABLE TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -7256,8 +7376,16 @@
           <t>0017550713-635-344716386342</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FENAMIC 250 MG CAP</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>FENAMIC 250 MG CAP detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7841,8 +7969,16 @@
           <t>1276227474-264-101329010845</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FER-IN-SOL DROPS 15MG-0.6ML (ELEMENTAL I</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>FER-IN-SOL DROPS 15MG-0.6ML (ELEMENTAL I detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8028,8 +8164,16 @@
           <t>0811969853-360-795396323002</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FEROSE - F TABLET</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>FEROSE - F TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8617,8 +8761,16 @@
           <t>5334414186-646-546296175992</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FENOGAL 200MG LIDOSE CAPSULES</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>FENOGAL 200MG LIDOSE CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -9200,8 +9352,16 @@
           <t>6041768256-472-483698409895</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLAMAZINE CREAM 1%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>FLAMAZINE CREAM 1% detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9586,8 +9746,16 @@
           <t>7639822267-594-696952908817</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUDARA 10MG F.C TABLETS</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>FLUDARA 10MG F.C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9968,8 +10136,16 @@
           <t>0084665729-085-091083761299</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUANXOL 3MG TAB</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>FLUANXOL 3MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10159,8 +10335,16 @@
           <t>6539236756-349-418174095680</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUANXOL 1MG TAB</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>FLUANXOL 1MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10346,8 +10530,16 @@
           <t>0336042451-381-406056366180</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUANXOL 0.5MG TAB</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>FLUANXOL 0.5MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10537,8 +10729,16 @@
           <t>4123711744-961-886062522308</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUDREX SYRUP</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>FLUDREX SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10935,8 +11135,16 @@
           <t>8338537027-041-247415172032</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUIMUCIL 100MG/1GM GRANULES FOR ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>FLUIMUCIL 100MG/1GM GRANULES FOR ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11130,8 +11338,16 @@
           <t>1020696596-574-460796397008</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUIMUCIL 200MG/1GM GRANULES FOR ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>FLUIMUCIL 200MG/1GM GRANULES FOR ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11321,8 +11537,16 @@
           <t>1483569392-926-800027731507</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUOXETIN HEXAL 20MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>FLUOXETIN HEXAL 20MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11508,8 +11732,16 @@
           <t>3772276891-203-491683179635</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUANXOL 0.5MG TAB</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>FLUANXOL 0.5MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11695,8 +11927,16 @@
           <t>8742048001-977-805085417626</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUORETS OPTH.STRIPS</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>FLUORETS OPTH.STRIPS detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -12081,8 +12321,16 @@
           <t>6322608997-054-814372016572</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLAMAZINE CREAM 1%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>FLAMAZINE CREAM 1% detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -13249,8 +13497,16 @@
           <t>5196038460-131-536803563784</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLECTOR EP TISSUGEL 1GM PATCHES</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>FLECTOR EP TISSUGEL 1GM PATCHES detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -14220,8 +14476,16 @@
           <t>5400988536-799-875959723118</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLIXOTIDE 2MG-2ML NEBULE</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>FLIXOTIDE 2MG-2ML NEBULE detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14600,8 +14864,16 @@
           <t>5812970286-008-492762526663</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLOXAPEN SYP 125MG-5ML</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>FLOXAPEN SYP 125MG-5ML detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14787,8 +15059,16 @@
           <t>2394317379-372-431307247597</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLOXAPEN CAPS 250MG</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>FLOXAPEN CAPS 250MG detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14974,8 +15254,16 @@
           <t>1322352509-510-092086310628</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLOXAPEN 500MG CAPS</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>FLOXAPEN 500MG CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15161,8 +15449,16 @@
           <t>3497491169-498-685200272135</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLOXAPEN 250MG-5ML POWD.FOR SUSP</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>FLOXAPEN 250MG-5ML POWD.FOR SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15951,8 +16247,16 @@
           <t>1120548852-375-553162783810</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLOCAZOLE 50 MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>FLOCAZOLE 50 MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16534,8 +16838,16 @@
           <t>5506584276-132-143628994573</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FATLOS 120MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>FATLOS 120MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -17720,8 +18032,16 @@
           <t>8228366273-261-107902959268</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EPIVIR 150MG F.C TABLET</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>EPIVIR 150MG F.C TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17915,8 +18235,16 @@
           <t>6332686405-492-206562834894</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EPIVIR 10 MG \ ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>EPIVIR 10 MG \ ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18106,8 +18434,16 @@
           <t>9313936287-524-239099193082</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EPIRAZOLE 20MG CAPS(E.C.PELLETS)</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>EPIRAZOLE 20MG CAPS(E.C.PELLETS) detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18691,8 +19027,16 @@
           <t>6192706058-336-130582220136</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EMICIPRO 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>EMICIPRO 500MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -19085,8 +19429,16 @@
           <t>7170644314-053-182325525309</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ELIQUIS 2.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ELIQUIS 2.5MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/23/file.xlsx
+++ b/product_upload/packages/23/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20446,7 +20446,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22068,7 +22068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22149,40 +22149,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22262,38 +22267,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>319.67</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-94D6C631925C</t>
         </is>
@@ -22373,38 +22383,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>97.52</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-AEA0E5B2D168</t>
         </is>
@@ -22484,38 +22499,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>321.52</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-BE91E9D44E51</t>
         </is>
@@ -22595,38 +22615,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>160.25</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-6973B2711E00</t>
         </is>
@@ -22706,38 +22731,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>75.02</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-1A7F5428904B</t>
         </is>
@@ -22817,38 +22847,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>87.31999999999999</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-520D237ECA5C</t>
         </is>
@@ -22928,38 +22963,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>346.59</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-08A4EFA26DA9</t>
         </is>
@@ -23039,38 +23079,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>400.07</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-9A9AF0A07574</t>
         </is>
@@ -23150,38 +23195,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>412.02</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-250755D40882</t>
         </is>
@@ -23261,38 +23311,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>151.15</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-0274421D4B29</t>
         </is>
@@ -23372,38 +23427,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>99.61</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-84FA23F2C6CE</t>
         </is>
@@ -23483,38 +23543,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>49.23</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-F838F5A07AB2</t>
         </is>
@@ -23594,38 +23659,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>396.34</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-92B81B8DD91C</t>
         </is>
@@ -23705,38 +23775,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>479.34</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-46604F479477</t>
         </is>
@@ -23816,38 +23891,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>106.97</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-B29E14704A7B</t>
         </is>
@@ -23927,38 +24007,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>417.45</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-BD9C1881593C</t>
         </is>
@@ -24038,38 +24123,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>396.95</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-7D8E2D68B638</t>
         </is>
@@ -24149,38 +24239,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>418.04</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-17771EC3D091</t>
         </is>
@@ -24260,38 +24355,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>351.94</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-9A58F4313A50</t>
         </is>
@@ -24371,38 +24471,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>252.36</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-B0D0E38D330F</t>
         </is>
